--- a/artfynd/A 56001-2025 artfynd.xlsx
+++ b/artfynd/A 56001-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,762 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129998417</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96390</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>A 56001, Äskedal, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>603578</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6423082</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129998330</v>
+      </c>
+      <c r="B4" t="n">
+        <v>105860</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 56001, Äskedal, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>603551</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6423053</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129998433</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57734</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 56001, Äskedal, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>603551</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6423053</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129998346</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56927</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>A 56001, Äskedal, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>603607</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6423085</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Drog iväg från marken, troligen tupp</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129998362</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>A 56001, Äskedal, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>603637</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6423085</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129998337</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98794</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>A 56001, Äskedal, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>603588</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6423043</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129998405</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57750</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 56001, Äskedal, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>603622</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6423107</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Flera bohål i murken sälg eller  björk Typiskt i klen död sälg el njörk.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56001-2025 artfynd.xlsx
+++ b/artfynd/A 56001-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129998417</v>
       </c>
       <c r="B3" t="n">
-        <v>96390</v>
+        <v>96393</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,46 +888,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129998330</v>
+        <v>129998433</v>
       </c>
       <c r="B4" t="n">
-        <v>105860</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -979,7 +975,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -998,42 +993,42 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129998433</v>
+        <v>129998346</v>
       </c>
       <c r="B5" t="n">
-        <v>57734</v>
+        <v>56930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1041,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603551</v>
+        <v>603607</v>
       </c>
       <c r="R5" t="n">
-        <v>6423053</v>
+        <v>6423085</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1077,6 +1072,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Drog iväg från marken, troligen tupp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,42 +1103,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129998346</v>
+        <v>129998362</v>
       </c>
       <c r="B6" t="n">
-        <v>56927</v>
+        <v>57898</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1146,7 +1150,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603607</v>
+        <v>603637</v>
       </c>
       <c r="R6" t="n">
         <v>6423085</v>
@@ -1182,11 +1186,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Drog iväg från marken, troligen tupp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,46 +1212,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129998362</v>
+        <v>129998330</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>105863</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1260,13 +1259,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603637</v>
+        <v>603551</v>
       </c>
       <c r="R7" t="n">
-        <v>6423085</v>
+        <v>6423053</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1304,6 +1303,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1325,7 +1325,7 @@
         <v>129998337</v>
       </c>
       <c r="B8" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>129998405</v>
       </c>
       <c r="B9" t="n">
-        <v>57750</v>
+        <v>57753</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 56001-2025 artfynd.xlsx
+++ b/artfynd/A 56001-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129998417</v>
       </c>
       <c r="B3" t="n">
-        <v>96393</v>
+        <v>96394</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>129998330</v>
       </c>
       <c r="B7" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>129998337</v>
       </c>
       <c r="B8" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56001-2025 artfynd.xlsx
+++ b/artfynd/A 56001-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129998417</v>
       </c>
       <c r="B3" t="n">
-        <v>96394</v>
+        <v>96411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129998362</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>129998330</v>
       </c>
       <c r="B7" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>129998337</v>
       </c>
       <c r="B8" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56001-2025 artfynd.xlsx
+++ b/artfynd/A 56001-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129998417</v>
       </c>
       <c r="B3" t="n">
-        <v>96427</v>
+        <v>96429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>129998330</v>
       </c>
       <c r="B7" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>129998337</v>
       </c>
       <c r="B8" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 56001-2025 artfynd.xlsx
+++ b/artfynd/A 56001-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>129998417</v>
       </c>
       <c r="B3" t="n">
-        <v>96429</v>
+        <v>96516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>129998433</v>
       </c>
       <c r="B4" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>129998346</v>
       </c>
       <c r="B5" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>129998362</v>
       </c>
       <c r="B6" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>129998330</v>
       </c>
       <c r="B7" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>129998337</v>
       </c>
       <c r="B8" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         <v>129998405</v>
       </c>
       <c r="B9" t="n">
-        <v>57754</v>
+        <v>57839</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 56001-2025 artfynd.xlsx
+++ b/artfynd/A 56001-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74843248</v>
+        <v>129998417</v>
       </c>
       <c r="B2" t="n">
-        <v>105644</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221141</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gullviva</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Primula veris</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>L4 Äskedal norra gdn 500 m SO, Sm</t>
+          <t>A 56001, Äskedal, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603700</v>
+        <v>603578</v>
       </c>
       <c r="R2" t="n">
-        <v>6422964</v>
+        <v>6423082</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1987-01-01</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1989-12-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Smålands flora 2007: KOO: 7H4b 3910. SOM: Primula veris. LEG: Margareta Arfwidsson</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,65 +758,56 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Bergig skogsmark</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Margareta Edqvist</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Margareta Edqvist</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Smålands flora (1978-2007)</t>
-        </is>
-      </c>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129998417</v>
+        <v>129998446</v>
       </c>
       <c r="B3" t="n">
-        <v>96516</v>
+        <v>79946</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -825,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603578</v>
+        <v>603657</v>
       </c>
       <c r="R3" t="n">
-        <v>6423082</v>
+        <v>6423004</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -863,11 +853,16 @@
           <t>2025-12-05</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På tallåga</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
@@ -888,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129998433</v>
+        <v>129998405</v>
       </c>
       <c r="B4" t="n">
-        <v>57823</v>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,16 +894,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -921,7 +916,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -931,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603551</v>
+        <v>603622</v>
       </c>
       <c r="R4" t="n">
-        <v>6423053</v>
+        <v>6423107</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -967,6 +962,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flera bohål i murken sälg eller  björk Typiskt i klen död sälg el njörk.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129998346</v>
+        <v>129998433</v>
       </c>
       <c r="B5" t="n">
-        <v>57016</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,31 +1004,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1036,13 +1036,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603607</v>
+        <v>603551</v>
       </c>
       <c r="R5" t="n">
-        <v>6423085</v>
+        <v>6423053</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1072,11 +1072,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Drog iväg från marken, troligen tupp</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,46 +1098,42 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129998362</v>
+        <v>129998346</v>
       </c>
       <c r="B6" t="n">
-        <v>57985</v>
+        <v>57141</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1150,7 +1141,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603637</v>
+        <v>603607</v>
       </c>
       <c r="R6" t="n">
         <v>6423085</v>
@@ -1186,6 +1177,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Drog iväg från marken, troligen tupp</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1212,46 +1208,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129998330</v>
+        <v>129998362</v>
       </c>
       <c r="B7" t="n">
-        <v>105987</v>
+        <v>58114</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1259,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603551</v>
+        <v>603637</v>
       </c>
       <c r="R7" t="n">
-        <v>6423053</v>
+        <v>6423085</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1303,7 +1299,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1325,7 +1320,7 @@
         <v>129998337</v>
       </c>
       <c r="B8" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1432,56 +1427,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129998405</v>
+        <v>74843248</v>
       </c>
       <c r="B9" t="n">
-        <v>57839</v>
+        <v>106155</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100048</v>
+        <v>221141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Gullviva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Primula veris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>A 56001, Äskedal, Sm</t>
+          <t>L4 Äskedal norra gdn 500 m SO, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603622</v>
+        <v>603700</v>
       </c>
       <c r="R9" t="n">
-        <v>6423107</v>
+        <v>6422964</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1505,17 +1492,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>1987-01-01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>1989-12-31</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Flera bohål i murken sälg eller  björk Typiskt i klen död sälg el njörk.</t>
+          <t>Smålands flora 2007: KOO: 7H4b 3910. SOM: Primula veris. LEG: Margareta Arfwidsson</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1526,19 +1513,138 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Bergig skogsmark</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Via Margareta Edqvist</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129998330</v>
+      </c>
+      <c r="B10" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>A 56001, Äskedal, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>603551</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6423053</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Loftahammar</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
